--- a/AAII_Financials/Quarterly/KLPPY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KLPPY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="92">
   <si>
     <t>KLPPY</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -655,7 +655,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -667,49 +667,64 @@
     <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -737,8 +752,20 @@
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -766,8 +793,20 @@
       <c r="K9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -795,8 +834,20 @@
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -808,8 +859,12 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -837,8 +892,20 @@
       <c r="K12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -866,8 +933,20 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -895,8 +974,20 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -924,8 +1015,20 @@
       <c r="K15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -934,8 +1037,12 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -963,8 +1070,20 @@
       <c r="K17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -992,8 +1111,20 @@
       <c r="K18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1005,8 +1136,12 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1034,8 +1169,20 @@
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1063,8 +1210,20 @@
       <c r="K21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1092,8 +1251,20 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1121,8 +1292,20 @@
       <c r="K23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1150,8 +1333,20 @@
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1179,8 +1374,20 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1208,8 +1415,20 @@
       <c r="K26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1237,8 +1456,20 @@
       <c r="K27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1266,8 +1497,20 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1295,8 +1538,20 @@
       <c r="K29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1324,8 +1579,20 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1353,8 +1620,20 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1382,8 +1661,20 @@
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1411,8 +1702,20 @@
       <c r="K33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1440,8 +1743,20 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1469,42 +1784,66 @@
       <c r="K35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1516,8 +1855,12 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1529,37 +1872,53 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>405600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>409300</v>
+      </c>
+      <c r="F41" s="3">
+        <v>976800</v>
+      </c>
+      <c r="G41" s="3">
+        <v>976100</v>
+      </c>
+      <c r="H41" s="3">
         <v>1124000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="I41" s="3">
         <v>1034500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="J41" s="3">
         <v>414900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="K41" s="3">
         <v>447000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="L41" s="3">
         <v>1029100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="M41" s="3">
         <v>1036200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="N41" s="3">
         <v>396500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="O41" s="3">
         <v>379700</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1587,37 +1946,61 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>424500</v>
+      </c>
+      <c r="E43" s="3">
+        <v>428500</v>
+      </c>
+      <c r="F43" s="3">
+        <v>257000</v>
+      </c>
+      <c r="G43" s="3">
+        <v>256800</v>
+      </c>
+      <c r="H43" s="3">
         <v>509600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="I43" s="3">
         <v>469000</v>
       </c>
-      <c r="F43" s="3">
-        <v>254600</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="J43" s="3">
+        <v>233800</v>
+      </c>
+      <c r="K43" s="3">
         <v>274300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="L43" s="3">
         <v>417000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="M43" s="3">
         <v>419900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="N43" s="3">
         <v>286400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="O43" s="3">
         <v>274200</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1645,153 +2028,225 @@
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>140600</v>
+      </c>
+      <c r="E45" s="3">
+        <v>141900</v>
+      </c>
+      <c r="F45" s="3">
+        <v>301900</v>
+      </c>
+      <c r="G45" s="3">
+        <v>301700</v>
+      </c>
+      <c r="H45" s="3">
         <v>145900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="I45" s="3">
         <v>134200</v>
       </c>
-      <c r="F45" s="3">
-        <v>272000</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="J45" s="3">
+        <v>292800</v>
+      </c>
+      <c r="K45" s="3">
         <v>293000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="L45" s="3">
         <v>77500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="M45" s="3">
         <v>78000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="N45" s="3">
         <v>318700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="O45" s="3">
         <v>305100</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>970800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>979700</v>
+      </c>
+      <c r="F46" s="3">
+        <v>1535600</v>
+      </c>
+      <c r="G46" s="3">
+        <v>1534600</v>
+      </c>
+      <c r="H46" s="3">
         <v>1779400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="I46" s="3">
         <v>1637700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="J46" s="3">
         <v>941500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="K46" s="3">
         <v>1014300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="L46" s="3">
         <v>1527200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="M46" s="3">
         <v>1537700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="N46" s="3">
         <v>1001500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="O46" s="3">
         <v>959000</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1278900</v>
+      </c>
+      <c r="E47" s="3">
+        <v>1290700</v>
+      </c>
+      <c r="F47" s="3">
+        <v>1279700</v>
+      </c>
+      <c r="G47" s="3">
+        <v>1278800</v>
+      </c>
+      <c r="H47" s="3">
         <v>1247000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="I47" s="3">
         <v>1147600</v>
       </c>
-      <c r="F47" s="3">
-        <v>1096600</v>
-      </c>
-      <c r="G47" s="3">
+      <c r="J47" s="3">
+        <v>1095100</v>
+      </c>
+      <c r="K47" s="3">
         <v>1181400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="L47" s="3">
         <v>1104100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="M47" s="3">
         <v>1111800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="N47" s="3">
         <v>1075500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="O47" s="3">
         <v>1029800</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>22468400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>22675700</v>
+      </c>
+      <c r="F48" s="3">
+        <v>22425700</v>
+      </c>
+      <c r="G48" s="3">
+        <v>22409900</v>
+      </c>
+      <c r="H48" s="3">
         <v>21745500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="I48" s="3">
         <v>20013300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="J48" s="3">
         <v>18878000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="K48" s="3">
         <v>20337200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="L48" s="3">
         <v>19205900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="M48" s="3">
         <v>19338500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="N48" s="3">
         <v>19243900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="O48" s="3">
         <v>18427200</v>
       </c>
     </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>578100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>583400</v>
+      </c>
+      <c r="F49" s="3">
+        <v>589300</v>
+      </c>
+      <c r="G49" s="3">
+        <v>588900</v>
+      </c>
+      <c r="H49" s="3">
         <v>586000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="I49" s="3">
         <v>539300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="J49" s="3">
         <v>507300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="K49" s="3">
         <v>546500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="L49" s="3">
         <v>526100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="M49" s="3">
         <v>529700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="N49" s="3">
         <v>541800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="O49" s="3">
         <v>518800</v>
       </c>
     </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1819,8 +2274,20 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1848,37 +2315,61 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>204500</v>
+      </c>
+      <c r="E52" s="3">
+        <v>206400</v>
+      </c>
+      <c r="F52" s="3">
+        <v>303000</v>
+      </c>
+      <c r="G52" s="3">
+        <v>302800</v>
+      </c>
+      <c r="H52" s="3">
         <v>321300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="I52" s="3">
         <v>295700</v>
       </c>
-      <c r="F52" s="3">
-        <v>271200</v>
-      </c>
-      <c r="G52" s="3">
+      <c r="J52" s="3">
+        <v>272700</v>
+      </c>
+      <c r="K52" s="3">
         <v>292200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="L52" s="3">
         <v>314400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="M52" s="3">
         <v>316500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="N52" s="3">
         <v>318900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="O52" s="3">
         <v>305400</v>
       </c>
     </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1906,37 +2397,61 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>25507400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>25742600</v>
+      </c>
+      <c r="F54" s="3">
+        <v>26145600</v>
+      </c>
+      <c r="G54" s="3">
+        <v>26127200</v>
+      </c>
+      <c r="H54" s="3">
         <v>25692900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="I54" s="3">
         <v>23646200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="J54" s="3">
         <v>21713300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="K54" s="3">
         <v>23391600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="L54" s="3">
         <v>22697000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="M54" s="3">
         <v>22853700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="N54" s="3">
         <v>22209400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="O54" s="3">
         <v>21266700</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1948,8 +2463,12 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1961,182 +2480,258 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>148200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>149500</v>
+      </c>
+      <c r="F57" s="3">
+        <v>112200</v>
+      </c>
+      <c r="G57" s="3">
+        <v>112200</v>
+      </c>
+      <c r="H57" s="3">
         <v>177900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="I57" s="3">
         <v>163700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="J57" s="3">
         <v>155600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="K57" s="3">
         <v>167600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="L57" s="3">
         <v>156400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="M57" s="3">
         <v>157500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="N57" s="3">
         <v>178600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="O57" s="3">
         <v>171000</v>
       </c>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2131300</v>
+      </c>
+      <c r="E58" s="3">
+        <v>2150900</v>
+      </c>
+      <c r="F58" s="3">
+        <v>1973300</v>
+      </c>
+      <c r="G58" s="3">
+        <v>1972000</v>
+      </c>
+      <c r="H58" s="3">
         <v>2298900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="I58" s="3">
         <v>2115800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="J58" s="3">
         <v>1425900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="K58" s="3">
         <v>1536100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="L58" s="3">
         <v>1856500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="M58" s="3">
         <v>1869300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="N58" s="3">
         <v>1771600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="O58" s="3">
         <v>1696400</v>
       </c>
     </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>735100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>741800</v>
+      </c>
+      <c r="F59" s="3">
+        <v>468400</v>
+      </c>
+      <c r="G59" s="3">
+        <v>468000</v>
+      </c>
+      <c r="H59" s="3">
         <v>839500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="I59" s="3">
         <v>772600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="J59" s="3">
         <v>430100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="K59" s="3">
         <v>463300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="L59" s="3">
         <v>722200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="M59" s="3">
         <v>727200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="N59" s="3">
         <v>421800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="O59" s="3">
         <v>403900</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3203500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>3233000</v>
+      </c>
+      <c r="F60" s="3">
+        <v>2725600</v>
+      </c>
+      <c r="G60" s="3">
+        <v>2723700</v>
+      </c>
+      <c r="H60" s="3">
         <v>3496900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="I60" s="3">
         <v>3218300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="J60" s="3">
         <v>2158700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="K60" s="3">
         <v>2325600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="L60" s="3">
         <v>2932400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="M60" s="3">
         <v>2952600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="N60" s="3">
         <v>2556400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="O60" s="3">
         <v>2447900</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7033900</v>
+      </c>
+      <c r="E61" s="3">
+        <v>7098800</v>
+      </c>
+      <c r="F61" s="3">
+        <v>8023400</v>
+      </c>
+      <c r="G61" s="3">
+        <v>8017700</v>
+      </c>
+      <c r="H61" s="3">
         <v>7729100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="I61" s="3">
         <v>7113400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="J61" s="3">
         <v>6955100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="K61" s="3">
         <v>7492600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="L61" s="3">
         <v>7465200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="M61" s="3">
         <v>7516800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="N61" s="3">
         <v>7035400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="O61" s="3">
         <v>6736800</v>
       </c>
     </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>295600</v>
+      </c>
+      <c r="E62" s="3">
+        <v>298300</v>
+      </c>
+      <c r="F62" s="3">
+        <v>322100</v>
+      </c>
+      <c r="G62" s="3">
+        <v>321800</v>
+      </c>
+      <c r="H62" s="3">
         <v>336900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="I62" s="3">
         <v>310100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="J62" s="3">
         <v>273300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="K62" s="3">
         <v>294400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="L62" s="3">
         <v>304800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="M62" s="3">
         <v>306900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="N62" s="3">
         <v>306400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="O62" s="3">
         <v>293400</v>
       </c>
     </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2164,8 +2759,20 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2193,8 +2800,20 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2222,37 +2841,61 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>12223700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>12336400</v>
+      </c>
+      <c r="F66" s="3">
+        <v>12685900</v>
+      </c>
+      <c r="G66" s="3">
+        <v>12677000</v>
+      </c>
+      <c r="H66" s="3">
         <v>13127400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="I66" s="3">
         <v>12081700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="J66" s="3">
         <v>10688200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="K66" s="3">
         <v>11514300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="L66" s="3">
         <v>11965200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="M66" s="3">
         <v>12047800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="N66" s="3">
         <v>11134300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="O66" s="3">
         <v>10661700</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2264,8 +2907,12 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2293,8 +2940,20 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2322,8 +2981,20 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2351,8 +3022,20 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2380,37 +3063,61 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4620800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>4663400</v>
+      </c>
+      <c r="F72" s="3">
+        <v>4849100</v>
+      </c>
+      <c r="G72" s="3">
+        <v>4845700</v>
+      </c>
+      <c r="H72" s="3">
         <v>4050100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="I72" s="3">
         <v>3727500</v>
       </c>
-      <c r="F72" s="3">
-        <v>1136200</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="J72" s="3">
+        <v>4614700</v>
+      </c>
+      <c r="K72" s="3">
         <v>1224100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="L72" s="3">
         <v>621100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="M72" s="3">
         <v>625400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="N72" s="3">
         <v>213000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="O72" s="3">
         <v>204000</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2438,8 +3145,20 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2467,8 +3186,20 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2496,37 +3227,61 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10821400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>10921200</v>
+      </c>
+      <c r="F76" s="3">
+        <v>10947500</v>
+      </c>
+      <c r="G76" s="3">
+        <v>10939800</v>
+      </c>
+      <c r="H76" s="3">
         <v>10155300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="I76" s="3">
         <v>9346300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="J76" s="3">
         <v>8901200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="K76" s="3">
         <v>9589200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="L76" s="3">
         <v>8618100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="M76" s="3">
         <v>8677600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="N76" s="3">
         <v>8861200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="O76" s="3">
         <v>8485100</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2554,42 +3309,66 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -2617,8 +3396,20 @@
       <c r="K81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2630,37 +3421,53 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+      <c r="N82" s="3"/>
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E83" s="3">
+        <v>4200</v>
+      </c>
+      <c r="F83" s="3">
+        <v>4700</v>
+      </c>
+      <c r="G83" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H83" s="3">
         <v>4300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="I83" s="3">
         <v>4300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="J83" s="3">
         <v>16300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="K83" s="3">
         <v>15600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="L83" s="3">
         <v>-6400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="M83" s="3">
         <v>-6400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="N83" s="3">
         <v>3700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="O83" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2688,8 +3495,20 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2717,8 +3536,20 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2746,8 +3577,20 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2775,8 +3618,20 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2804,37 +3659,61 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>292000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>294700</v>
+      </c>
+      <c r="F89" s="3">
+        <v>292400</v>
+      </c>
+      <c r="G89" s="3">
+        <v>292200</v>
+      </c>
+      <c r="H89" s="3">
         <v>309500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="I89" s="3">
         <v>284900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="J89" s="3">
         <v>240200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="K89" s="3">
         <v>258800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="L89" s="3">
         <v>268300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="M89" s="3">
         <v>270200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="N89" s="3">
         <v>258100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="O89" s="3">
         <v>247100</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2846,37 +3725,53 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+      <c r="N90" s="3"/>
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-6100</v>
+        <v>-3700</v>
       </c>
       <c r="E91" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="F91" s="3">
         <v>-5600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="J91" s="3">
         <v>-4600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="K91" s="3">
         <v>-4900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="L91" s="3">
         <v>-2300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="M91" s="3">
         <v>-2300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="N91" s="3">
         <v>-3400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="O91" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2904,8 +3799,20 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2933,37 +3840,61 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-47100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-47600</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-108900</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-108800</v>
+      </c>
+      <c r="H94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="I94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="J94" s="3">
         <v>-19200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="K94" s="3">
         <v>-20700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="L94" s="3">
         <v>-127800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="M94" s="3">
         <v>-128700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="N94" s="3">
         <v>1700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="O94" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2975,37 +3906,53 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+      <c r="N95" s="3"/>
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>155400</v>
+      </c>
+      <c r="E96" s="3">
+        <v>156800</v>
+      </c>
+      <c r="F96" s="3">
+        <v>155500</v>
+      </c>
+      <c r="G96" s="3">
         <v>155300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="H96" s="3">
+        <v>155300</v>
+      </c>
+      <c r="I96" s="3">
         <v>142900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="J96" s="3">
         <v>118100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="K96" s="3">
         <v>127300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="L96" s="3">
         <v>137700</v>
       </c>
-      <c r="I96" s="3">
+      <c r="M96" s="3">
         <v>138600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="N96" s="3">
         <v>5700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="O96" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3033,8 +3980,20 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3062,8 +4021,20 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3091,91 +4062,139 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-520100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-524900</v>
+      </c>
+      <c r="F100" s="3">
+        <v>-254100</v>
+      </c>
+      <c r="G100" s="3">
+        <v>-253900</v>
+      </c>
+      <c r="H100" s="3">
         <v>18400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="I100" s="3">
         <v>16900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="J100" s="3">
         <v>-510000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="K100" s="3">
         <v>-549400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="L100" s="3">
         <v>181600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="M100" s="3">
         <v>182800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="N100" s="3">
         <v>-248400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="O100" s="3">
         <v>-237800</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>4</v>
+      <c r="D101" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-1300</v>
       </c>
       <c r="F101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="G101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3">
         <v>200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="K101" s="3">
         <v>200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="L101" s="3">
         <v>-800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="M101" s="3">
         <v>-800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="N101" s="3">
         <v>-400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="O101" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-272200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-274700</v>
+      </c>
+      <c r="F102" s="3">
+        <v>-73400</v>
+      </c>
+      <c r="G102" s="3">
+        <v>-73400</v>
+      </c>
+      <c r="H102" s="3">
         <v>326400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="I102" s="3">
         <v>300400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="J102" s="3">
         <v>-289400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="K102" s="3">
         <v>-311800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="L102" s="3">
         <v>322100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="M102" s="3">
         <v>324400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="N102" s="3">
         <v>11600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="O102" s="3">
         <v>11100</v>
       </c>
     </row>
